--- a/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
+++ b/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:30:51+00:00</t>
+    <t>2026-06-19T01:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
+++ b/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T01:46:09+00:00</t>
+    <t>2026-06-19T03:25:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
+++ b/previews/pr-1074/milestone/fhir/6.0.1-ci-build/CodeSystem-medication-type.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T03:25:57+00:00</t>
+    <t>2026-06-19T08:07:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
